--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9732,0.0036,0.0194,0.0028</t>
-  </si>
-  <si>
-    <t>0.0069,0.0018,0.0002,0.9973</t>
-  </si>
-  <si>
-    <t>0.6503,0.0032,0.0011,0.5182</t>
-  </si>
-  <si>
-    <t>0.1059,0.0001,0.0005,0.9642</t>
-  </si>
-  <si>
-    <t>0.9979,0.0010,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9148,0.0104,0.0156,0.0554</t>
+  </si>
+  <si>
+    <t>0.0029,0.0007,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.9073,0.0005,0.0004,0.1945</t>
+  </si>
+  <si>
+    <t>0.1093,0.0013,0.0020,0.9562</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0011,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0015,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.8231,0.0919,0.0648,0.0070</t>
+  </si>
+  <si>
+    <t>0.3029,0.0022,0.7711,0.0040</t>
+  </si>
+  <si>
+    <t>0.1650,0.0292,0.8475,0.0038</t>
+  </si>
+  <si>
+    <t>0.0304,0.0033,0.9746,0.0010</t>
+  </si>
+  <si>
+    <t>0.9942,0.0005,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9969,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.9960,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.1778,0.8999,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.0196,0.9717,0.0082,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.9973,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.2769,0.0038,0.8021,0.0038</t>
+  </si>
+  <si>
+    <t>0.2037,0.0139,0.8063,0.0116</t>
+  </si>
+  <si>
+    <t>0.0073,0.0002,0.9839,0.0054</t>
+  </si>
+  <si>
+    <t>0.0860,0.0008,0.9337,0.0021</t>
+  </si>
+  <si>
+    <t>0.2897,0.0031,0.8049,0.0012</t>
+  </si>
+  <si>
+    <t>0.1094,0.0002,0.9620,0.0001</t>
+  </si>
+  <si>
+    <t>0.0062,0.0042,0.9856,0.0098</t>
+  </si>
+  <si>
+    <t>0.9479,0.0807,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.8453,0.1003,0.0770,0.0055</t>
+  </si>
+  <si>
+    <t>0.0133,0.0104,0.9826,0.0024</t>
+  </si>
+  <si>
+    <t>0.0156,0.7193,0.4120,0.0012</t>
+  </si>
+  <si>
+    <t>0.9747,0.0130,0.0077,0.0022</t>
+  </si>
+  <si>
+    <t>0.9561,0.0350,0.0131,0.0010</t>
+  </si>
+  <si>
+    <t>0.7623,0.3387,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.0106,0.9845,0.1517,0.0013</t>
+  </si>
+  <si>
+    <t>0.0174,0.0297,0.9091,0.0426</t>
+  </si>
+  <si>
+    <t>0.0643,0.1875,0.8712,0.0440</t>
+  </si>
+  <si>
+    <t>0.0210,0.0145,0.9718,0.0049</t>
+  </si>
+  <si>
+    <t>0.1523,0.0031,0.9198,0.0016</t>
+  </si>
+  <si>
+    <t>0.2014,0.0067,0.9230,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.9540,0.0136,0.0038</t>
+  </si>
+  <si>
+    <t>0.0644,0.0186,0.9512,0.0027</t>
+  </si>
+  <si>
+    <t>0.1282,0.0455,0.0160,0.8931</t>
+  </si>
+  <si>
+    <t>0.0028,0.8916,0.0089,0.1808</t>
+  </si>
+  <si>
+    <t>0.0007,0.9959,0.0232,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.9955,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.0096,0.0167,0.9773,0.0095</t>
+  </si>
+  <si>
+    <t>0.0031,0.1838,0.9891,0.0009</t>
+  </si>
+  <si>
+    <t>0.0189,0.0012,0.9746,0.0071</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9887,0.1210</t>
+  </si>
+  <si>
+    <t>0.0071,0.0030,0.9844,0.0041</t>
+  </si>
+  <si>
+    <t>0.0074,0.0046,0.9890,0.0021</t>
+  </si>
+  <si>
+    <t>0.9838,0.0190,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.9766,0.0029,0.0196,0.0019</t>
+  </si>
+  <si>
+    <t>0.9869,0.0083,0.0015,0.0014</t>
+  </si>
+  <si>
+    <t>0.0139,0.0691,0.9695,0.0189</t>
+  </si>
+  <si>
+    <t>0.9920,0.0042,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.8745,0.8666,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.0436,0.9754,0.0123</t>
+  </si>
+  <si>
+    <t>0.0176,0.0067,0.9824,0.0021</t>
+  </si>
+  <si>
+    <t>0.0036,0.6925,0.9528,0.0021</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9968,0.0023</t>
+  </si>
+  <si>
+    <t>0.0143,0.9838,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0059,0.9902,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9724,0.0023,0.0487,0.0006</t>
+  </si>
+  <si>
+    <t>0.5659,0.0441,0.5894,0.0046</t>
+  </si>
+  <si>
+    <t>0.0047,0.0085,0.9886,0.0038</t>
+  </si>
+  <si>
+    <t>0.0039,0.8492,0.9371,0.0008</t>
+  </si>
+  <si>
+    <t>0.0073,0.6276,0.8725,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0351,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9950,0.3414,0.0030</t>
+  </si>
+  <si>
+    <t>0.0396,0.0021,0.0138,0.9614</t>
+  </si>
+  <si>
+    <t>0.0008,0.0010,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0015,0.0018,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.0163,0.0013,0.0004,0.9929</t>
+  </si>
+  <si>
+    <t>0.0118,0.0005,0.0014,0.9933</t>
+  </si>
+  <si>
+    <t>0.0013,0.0016,0.0008,0.9983</t>
+  </si>
+  <si>
+    <t>0.0035,0.9797,0.1103,0.0076</t>
+  </si>
+  <si>
+    <t>0.0014,0.9386,0.9779,0.0005</t>
+  </si>
+  <si>
+    <t>0.0031,0.9577,0.5240,0.0009</t>
+  </si>
+  <si>
+    <t>0.0085,0.9089,0.6333,0.0031</t>
+  </si>
+  <si>
+    <t>0.0004,0.9840,0.9684,0.0002</t>
+  </si>
+  <si>
+    <t>0.0065,0.1074,0.9606,0.0016</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0019,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9889,0.0106,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0011,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9904,0.0047,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0032,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0018,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0762,0.0007,0.9525,0.0005</t>
+  </si>
+  <si>
+    <t>0.0177,0.0011,0.9886,0.0003</t>
+  </si>
+  <si>
+    <t>0.9911,0.0007,0.0073,0.0003</t>
+  </si>
+  <si>
+    <t>0.0192,0.0027,0.9777,0.0025</t>
+  </si>
+  <si>
+    <t>0.0039,0.9936,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0092,0.9754,0.0059,0.0054</t>
+  </si>
+  <si>
+    <t>0.0040,0.9897,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.9976,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9982,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9400,0.0445,0.0057,0.0075</t>
+  </si>
+  <si>
+    <t>0.9046,0.0173,0.0913,0.0054</t>
+  </si>
+  <si>
+    <t>0.1814,0.0071,0.8616,0.0042</t>
+  </si>
+  <si>
+    <t>0.6360,0.0275,0.4090,0.0055</t>
+  </si>
+  <si>
+    <t>0.3251,0.0091,0.7885,0.0054</t>
+  </si>
+  <si>
+    <t>0.0140,0.0176,0.2656,0.9034</t>
+  </si>
+  <si>
+    <t>0.0037,0.9764,0.0064,0.0035</t>
+  </si>
+  <si>
+    <t>0.0004,0.9961,0.0078,0.0015</t>
+  </si>
+  <si>
+    <t>0.0007,0.9920,0.0005,0.0746</t>
+  </si>
+  <si>
+    <t>0.0002,0.9096,0.9894,0.0006</t>
+  </si>
+  <si>
+    <t>0.0074,0.9922,0.0104,0.0003</t>
+  </si>
+  <si>
+    <t>0.9823,0.0214,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.8456,0.2625,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9944,0.0007,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9968,0.0003,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9955,0.0008,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9929,0.0026,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.0088,0.4218,0.9000,0.0102</t>
+  </si>
+  <si>
+    <t>0.0161,0.4803,0.8511,0.0026</t>
+  </si>
+  <si>
+    <t>0.0636,0.0032,0.9643,0.0003</t>
+  </si>
+  <si>
+    <t>0.0186,0.0264,0.9601,0.0048</t>
+  </si>
+  <si>
+    <t>0.9764,0.0060,0.0048,0.0041</t>
+  </si>
+  <si>
+    <t>0.8771,0.0073,0.1687,0.0076</t>
+  </si>
+  <si>
+    <t>0.2946,0.0009,0.8381,0.0018</t>
+  </si>
+  <si>
+    <t>0.9490,0.0057,0.0651,0.0011</t>
+  </si>
+  <si>
+    <t>0.1725,0.0053,0.0006,0.8979</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0005,0.0266,0.0005,0.9982</t>
+  </si>
+  <si>
+    <t>0.0063,0.0002,0.0007,0.9966</t>
+  </si>
+  <si>
+    <t>0.0020,0.3656,0.9070,0.0360</t>
+  </si>
+  <si>
+    <t>0.9937,0.0026,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.0851,0.9277,0.0058,0.0159</t>
+  </si>
+  <si>
+    <t>0.9949,0.0005,0.0003,0.0035</t>
+  </si>
+  <si>
+    <t>0.0813,0.9270,0.0190,0.0039</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.8892,0.0044,0.0020,0.1747</t>
+  </si>
+  <si>
+    <t>0.9928,0.0027,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0009,0.0021,0.9789,0.1785</t>
+  </si>
+  <si>
+    <t>0.9308,0.0002,0.0011,0.0931</t>
+  </si>
+  <si>
+    <t>0.9504,0.0022,0.0037,0.0503</t>
+  </si>
+  <si>
+    <t>0.7186,0.4099,0.0055,0.0016</t>
+  </si>
+  <si>
+    <t>0.9220,0.0101,0.0626,0.0041</t>
+  </si>
+  <si>
+    <t>0.9819,0.0117,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.1418,0.8795,0.0047,0.0020</t>
+  </si>
+  <si>
+    <t>0.8838,0.0178,0.1283,0.0020</t>
+  </si>
+  <si>
+    <t>0.9740,0.0094,0.0045,0.0041</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0018,0.0004,0.0039</t>
+  </si>
+  <si>
+    <t>0.9922,0.0024,0.0036,0.0007</t>
   </si>
   <si>
     <t>0.9989,0.0001,0.0001,0.0005</t>
   </si>
   <si>
-    <t>0.9989,0.0001,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0011,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0001,0.0002</t>
+    <t>0.9905,0.0024,0.0021,0.0029</t>
+  </si>
+  <si>
+    <t>0.9970,0.0024,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0004,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9406,0.0595,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.6013,0.5143,0.0078,0.0010</t>
+  </si>
+  <si>
+    <t>0.7683,0.2695,0.0057,0.0037</t>
+  </si>
+  <si>
+    <t>0.0272,0.4356,0.9321,0.0018</t>
+  </si>
+  <si>
+    <t>0.9658,0.0374,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9897,0.0043,0.0021,0.0018</t>
+  </si>
+  <si>
+    <t>0.9635,0.0223,0.0054,0.0052</t>
+  </si>
+  <si>
+    <t>0.9482,0.0507,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.0081,0.0150,0.9922,0.0013</t>
+  </si>
+  <si>
+    <t>0.9662,0.0100,0.0204,0.0010</t>
+  </si>
+  <si>
+    <t>0.0089,0.0068,0.9876,0.0035</t>
+  </si>
+  <si>
+    <t>0.0594,0.0762,0.9178,0.0214</t>
+  </si>
+  <si>
+    <t>0.0040,0.0005,0.9943,0.0012</t>
+  </si>
+  <si>
+    <t>0.0290,0.0226,0.9512,0.0035</t>
+  </si>
+  <si>
+    <t>0.0097,0.0158,0.9909,0.0005</t>
+  </si>
+  <si>
+    <t>0.0096,0.0003,0.9935,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.0139,0.9911,0.0063</t>
+  </si>
+  <si>
+    <t>0.1931,0.0177,0.7571,0.0541</t>
+  </si>
+  <si>
+    <t>0.1064,0.0057,0.9394,0.0013</t>
+  </si>
+  <si>
+    <t>0.1328,0.0256,0.8331,0.0380</t>
+  </si>
+  <si>
+    <t>0.2015,0.2874,0.4629,0.0162</t>
+  </si>
+  <si>
+    <t>0.6895,0.0135,0.3767,0.0033</t>
+  </si>
+  <si>
+    <t>0.5851,0.3547,0.0275,0.0059</t>
+  </si>
+  <si>
+    <t>0.8931,0.0226,0.0703,0.0145</t>
+  </si>
+  <si>
+    <t>0.5018,0.0086,0.4453,0.0283</t>
+  </si>
+  <si>
+    <t>0.0552,0.9336,0.0129,0.0060</t>
+  </si>
+  <si>
+    <t>0.0944,0.9422,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.6935,0.4743,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9594,0.0540,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.6261,0.5164,0.0073,0.0015</t>
+  </si>
+  <si>
+    <t>0.9325,0.0119,0.0429,0.0067</t>
+  </si>
+  <si>
+    <t>0.9119,0.0007,0.1484,0.0009</t>
+  </si>
+  <si>
+    <t>0.9748,0.0018,0.0088,0.0072</t>
+  </si>
+  <si>
+    <t>0.8963,0.0072,0.1598,0.0032</t>
+  </si>
+  <si>
+    <t>0.8523,0.0008,0.1924,0.0039</t>
+  </si>
+  <si>
+    <t>0.0032,0.0049,0.9843,0.0337</t>
+  </si>
+  <si>
+    <t>0.0693,0.0212,0.9085,0.0263</t>
+  </si>
+  <si>
+    <t>0.0444,0.0122,0.9655,0.0029</t>
+  </si>
+  <si>
+    <t>0.6396,0.0107,0.5006,0.0014</t>
+  </si>
+  <si>
+    <t>0.0123,0.2811,0.7007,0.0082</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9845,0.0100,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9940,0.0023,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0024,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0097,0.0298,0.9731,0.0149</t>
+  </si>
+  <si>
+    <t>0.3834,0.1190,0.5654,0.0442</t>
+  </si>
+  <si>
+    <t>0.9549,0.0005,0.0158,0.0070</t>
+  </si>
+  <si>
+    <t>0.0224,0.0031,0.9769,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.0085,0.9882,0.0054</t>
+  </si>
+  <si>
+    <t>0.0017,0.0254,0.9898,0.0102</t>
+  </si>
+  <si>
+    <t>0.0023,0.0014,0.9963,0.0006</t>
+  </si>
+  <si>
+    <t>0.0262,0.0170,0.9342,0.0053</t>
+  </si>
+  <si>
+    <t>0.0013,0.0117,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0104,0.0074,0.9852,0.0041</t>
+  </si>
+  <si>
+    <t>0.0144,0.0322,0.9664,0.0050</t>
+  </si>
+  <si>
+    <t>0.5495,0.0119,0.5423,0.0138</t>
+  </si>
+  <si>
+    <t>0.8888,0.0008,0.2031,0.0014</t>
+  </si>
+  <si>
+    <t>0.9895,0.0007,0.0062,0.0010</t>
   </si>
   <si>
     <t>0.9991,0.0001,0.0001,0.0003</t>
   </si>
   <si>
-    <t>0.9989,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9618,0.0060,0.0215,0.0039</t>
-  </si>
-  <si>
-    <t>0.1343,0.0035,0.9281,0.0009</t>
-  </si>
-  <si>
-    <t>0.4646,0.0040,0.7520,0.0001</t>
-  </si>
-  <si>
-    <t>0.0241,0.0019,0.9761,0.0013</t>
-  </si>
-  <si>
-    <t>0.9569,0.0049,0.0596,0.0014</t>
-  </si>
-  <si>
-    <t>0.0007,0.9982,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9975,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.5575,0.6328,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0090,0.9817,0.0045,0.0027</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.2321,0.0109,0.8514,0.0043</t>
-  </si>
-  <si>
-    <t>0.8177,0.0323,0.1142,0.0453</t>
-  </si>
-  <si>
-    <t>0.0117,0.0004,0.9780,0.0061</t>
-  </si>
-  <si>
-    <t>0.0081,0.0016,0.9893,0.0015</t>
-  </si>
-  <si>
-    <t>0.1756,0.0002,0.9250,0.0001</t>
-  </si>
-  <si>
-    <t>0.0225,0.0004,0.9862,0.0004</t>
-  </si>
-  <si>
-    <t>0.0047,0.0009,0.9915,0.0038</t>
-  </si>
-  <si>
-    <t>0.4390,0.6479,0.0046,0.0027</t>
-  </si>
-  <si>
-    <t>0.7578,0.0521,0.2053,0.0376</t>
-  </si>
-  <si>
-    <t>0.0023,0.0068,0.9888,0.0129</t>
-  </si>
-  <si>
-    <t>0.0131,0.7734,0.6675,0.0012</t>
-  </si>
-  <si>
-    <t>0.9865,0.0173,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.8822,0.0756,0.0304,0.0008</t>
-  </si>
-  <si>
-    <t>0.8097,0.3191,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0070,0.9871,0.0639,0.0041</t>
-  </si>
-  <si>
-    <t>0.0722,0.3155,0.2070,0.0791</t>
-  </si>
-  <si>
-    <t>0.0322,0.0015,0.9791,0.0016</t>
-  </si>
-  <si>
-    <t>0.0348,0.0224,0.9748,0.0016</t>
-  </si>
-  <si>
-    <t>0.0282,0.0028,0.9677,0.0066</t>
-  </si>
-  <si>
-    <t>0.0302,0.0214,0.9792,0.0008</t>
-  </si>
-  <si>
-    <t>0.0023,0.9942,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0173,0.0063,0.9799,0.0027</t>
-  </si>
-  <si>
-    <t>0.0031,0.6653,0.0025,0.9600</t>
-  </si>
-  <si>
-    <t>0.0037,0.9667,0.0033,0.0099</t>
-  </si>
-  <si>
-    <t>0.0007,0.9938,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.9950,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.0058,0.0146,0.9856,0.0041</t>
-  </si>
-  <si>
-    <t>0.0032,0.0765,0.9906,0.0010</t>
-  </si>
-  <si>
-    <t>0.2136,0.0007,0.8737,0.0014</t>
-  </si>
-  <si>
-    <t>0.0022,0.0005,0.9947,0.0040</t>
-  </si>
-  <si>
-    <t>0.0052,0.0019,0.9901,0.0021</t>
-  </si>
-  <si>
-    <t>0.0041,0.0060,0.9861,0.0050</t>
-  </si>
-  <si>
-    <t>0.9904,0.0054,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.9793,0.0074,0.0035,0.0065</t>
-  </si>
-  <si>
-    <t>0.0040,0.0122,0.9916,0.0070</t>
-  </si>
-  <si>
-    <t>0.9936,0.0007,0.0005,0.0039</t>
-  </si>
-  <si>
-    <t>0.9944,0.0013,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.9962,0.0007,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.0012,0.9403,0.9694,0.0005</t>
-  </si>
-  <si>
-    <t>0.0057,0.0153,0.9757,0.0126</t>
-  </si>
-  <si>
-    <t>0.0123,0.0077,0.9828,0.0014</t>
-  </si>
-  <si>
-    <t>0.0012,0.8784,0.9711,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9963,0.0021</t>
-  </si>
-  <si>
-    <t>0.0184,0.9763,0.0146,0.0005</t>
-  </si>
-  <si>
-    <t>0.0116,0.9821,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.2937,0.0152,0.8398,0.0046</t>
-  </si>
-  <si>
-    <t>0.6620,0.1271,0.1864,0.0009</t>
-  </si>
-  <si>
-    <t>0.0017,0.0042,0.9948,0.0027</t>
-  </si>
-  <si>
-    <t>0.0007,0.9261,0.9854,0.0003</t>
-  </si>
-  <si>
-    <t>0.0054,0.4506,0.9035,0.0058</t>
-  </si>
-  <si>
-    <t>0.0003,0.9980,0.1684,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9660,0.9518,0.0008</t>
-  </si>
-  <si>
-    <t>0.0095,0.0055,0.0038,0.9911</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0083,0.0001,0.0000,0.9982</t>
-  </si>
-  <si>
-    <t>0.0100,0.0010,0.0012,0.9940</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0060,0.0001,0.0005,0.9966</t>
-  </si>
-  <si>
-    <t>0.0018,0.9840,0.1660,0.0009</t>
-  </si>
-  <si>
-    <t>0.0010,0.9453,0.9849,0.0003</t>
-  </si>
-  <si>
-    <t>0.0044,0.9706,0.3883,0.0008</t>
-  </si>
-  <si>
-    <t>0.0178,0.4939,0.8200,0.0258</t>
-  </si>
-  <si>
-    <t>0.0012,0.9708,0.9333,0.0005</t>
-  </si>
-  <si>
-    <t>0.0110,0.5772,0.8008,0.0023</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9909,0.0059,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9824,0.0214,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9956,0.0017,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9970,0.0029,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0013,0.0006,0.0018</t>
-  </si>
-  <si>
-    <t>0.9942,0.0035,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.0116,0.0015,0.9818,0.0018</t>
-  </si>
-  <si>
-    <t>0.1456,0.0126,0.9138,0.0011</t>
-  </si>
-  <si>
-    <t>0.9884,0.0012,0.0044,0.0011</t>
-  </si>
-  <si>
-    <t>0.0043,0.0070,0.9932,0.0016</t>
-  </si>
-  <si>
-    <t>0.0006,0.9980,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0216,0.9576,0.0069,0.0141</t>
-  </si>
-  <si>
-    <t>0.0279,0.9584,0.0062,0.0023</t>
-  </si>
-  <si>
-    <t>0.0022,0.9954,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.9952,0.0049,0.0022</t>
-  </si>
-  <si>
-    <t>0.7193,0.3160,0.0098,0.0023</t>
-  </si>
-  <si>
-    <t>0.9095,0.0099,0.1060,0.0058</t>
-  </si>
-  <si>
-    <t>0.1686,0.0105,0.8473,0.0091</t>
-  </si>
-  <si>
-    <t>0.5768,0.0142,0.4319,0.0273</t>
-  </si>
-  <si>
-    <t>0.5841,0.0084,0.5806,0.0049</t>
-  </si>
-  <si>
-    <t>0.0026,0.0683,0.0029,0.9912</t>
-  </si>
-  <si>
-    <t>0.0032,0.9853,0.0033,0.0026</t>
-  </si>
-  <si>
-    <t>0.0002,0.9972,0.0149,0.0026</t>
-  </si>
-  <si>
-    <t>0.0017,0.9881,0.0007,0.0712</t>
-  </si>
-  <si>
-    <t>0.0003,0.9541,0.9893,0.0002</t>
-  </si>
-  <si>
-    <t>0.0071,0.9901,0.0061,0.0006</t>
-  </si>
-  <si>
-    <t>0.9866,0.0175,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9190,0.0971,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0008,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9968,0.0004,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.0114,0.3029,0.9519,0.0020</t>
-  </si>
-  <si>
-    <t>0.0778,0.3227,0.8601,0.0080</t>
-  </si>
-  <si>
-    <t>0.0776,0.0113,0.9469,0.0005</t>
-  </si>
-  <si>
-    <t>0.1128,0.0030,0.9274,0.0013</t>
-  </si>
-  <si>
-    <t>0.9829,0.0046,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.7423,0.0052,0.2257,0.0267</t>
-  </si>
-  <si>
-    <t>0.6946,0.0005,0.4516,0.0020</t>
-  </si>
-  <si>
-    <t>0.8578,0.0064,0.1780,0.0089</t>
-  </si>
-  <si>
-    <t>0.0677,0.0005,0.0002,0.9802</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0036,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0085,0.0003,0.0003,0.9963</t>
-  </si>
-  <si>
-    <t>0.0010,0.9297,0.6354,0.0055</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0642,0.9232,0.0208,0.0392</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.4611,0.5684,0.0023,0.0075</t>
-  </si>
-  <si>
-    <t>0.9971,0.0006,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.7292,0.0009,0.0035,0.4664</t>
-  </si>
-  <si>
-    <t>0.9861,0.0047,0.0027,0.0030</t>
-  </si>
-  <si>
-    <t>0.0003,0.0012,0.9870,0.1443</t>
-  </si>
-  <si>
-    <t>0.9931,0.0001,0.0001,0.0061</t>
-  </si>
-  <si>
-    <t>0.9909,0.0006,0.0002,0.0066</t>
-  </si>
-  <si>
-    <t>0.7974,0.1295,0.0666,0.0046</t>
-  </si>
-  <si>
-    <t>0.9375,0.0109,0.0238,0.0185</t>
-  </si>
-  <si>
-    <t>0.9908,0.0024,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.6699,0.2332,0.0735,0.0220</t>
-  </si>
-  <si>
-    <t>0.4052,0.0174,0.6453,0.0034</t>
-  </si>
-  <si>
-    <t>0.9653,0.0074,0.0280,0.0020</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0011,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9913,0.0032,0.0022,0.0014</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9868,0.0050,0.0037,0.0032</t>
-  </si>
-  <si>
-    <t>0.9956,0.0027,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0002,0.0029</t>
-  </si>
-  <si>
-    <t>0.8824,0.1091,0.0012,0.0065</t>
-  </si>
-  <si>
-    <t>0.6075,0.4885,0.0048,0.0039</t>
-  </si>
-  <si>
-    <t>0.5086,0.5759,0.0051,0.0031</t>
-  </si>
-  <si>
-    <t>0.9813,0.0118,0.0083,0.0017</t>
-  </si>
-  <si>
-    <t>0.9369,0.0791,0.0015,0.0013</t>
-  </si>
-  <si>
-    <t>0.9852,0.0031,0.0016,0.0074</t>
-  </si>
-  <si>
-    <t>0.9925,0.0010,0.0017,0.0028</t>
-  </si>
-  <si>
-    <t>0.9850,0.0133,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0181,0.9951,0.0017</t>
-  </si>
-  <si>
-    <t>0.9522,0.0329,0.0188,0.0010</t>
-  </si>
-  <si>
-    <t>0.0108,0.0030,0.9913,0.0004</t>
-  </si>
-  <si>
-    <t>0.0172,0.0193,0.9756,0.0045</t>
-  </si>
-  <si>
-    <t>0.0048,0.0146,0.9845,0.0105</t>
-  </si>
-  <si>
-    <t>0.0149,0.0190,0.9851,0.0002</t>
-  </si>
-  <si>
-    <t>0.2551,0.0037,0.8908,0.0002</t>
-  </si>
-  <si>
-    <t>0.0045,0.0003,0.9929,0.0016</t>
-  </si>
-  <si>
-    <t>0.0047,0.0126,0.9909,0.0044</t>
-  </si>
-  <si>
-    <t>0.0832,0.0027,0.9124,0.0105</t>
-  </si>
-  <si>
-    <t>0.4412,0.0018,0.6856,0.0031</t>
-  </si>
-  <si>
-    <t>0.2592,0.0138,0.7713,0.0073</t>
-  </si>
-  <si>
-    <t>0.3927,0.0299,0.6896,0.0070</t>
-  </si>
-  <si>
-    <t>0.2510,0.0204,0.8300,0.0032</t>
-  </si>
-  <si>
-    <t>0.9084,0.0079,0.1050,0.0008</t>
-  </si>
-  <si>
-    <t>0.9195,0.0075,0.0760,0.0066</t>
-  </si>
-  <si>
-    <t>0.2143,0.0030,0.8088,0.0104</t>
-  </si>
-  <si>
-    <t>0.0123,0.9862,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.0561,0.9443,0.0075,0.0030</t>
-  </si>
-  <si>
-    <t>0.8133,0.4041,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0044,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.8737,0.1995,0.0047,0.0020</t>
-  </si>
-  <si>
-    <t>0.9472,0.0107,0.0424,0.0006</t>
-  </si>
-  <si>
-    <t>0.9836,0.0008,0.0147,0.0015</t>
-  </si>
-  <si>
-    <t>0.9164,0.0026,0.0244,0.0387</t>
-  </si>
-  <si>
-    <t>0.9432,0.0030,0.0699,0.0020</t>
-  </si>
-  <si>
-    <t>0.5169,0.0076,0.5287,0.0108</t>
-  </si>
-  <si>
-    <t>0.0076,0.0068,0.9716,0.0331</t>
-  </si>
-  <si>
-    <t>0.0857,0.0113,0.8927,0.0242</t>
-  </si>
-  <si>
-    <t>0.1785,0.0129,0.8517,0.0034</t>
-  </si>
-  <si>
-    <t>0.4228,0.0091,0.6861,0.0018</t>
-  </si>
-  <si>
-    <t>0.0280,0.0403,0.9453,0.0110</t>
-  </si>
-  <si>
-    <t>0.9965,0.0011,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0009,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9972,0.0021,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9968,0.0018,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0282,0.0589,0.9420,0.0248</t>
-  </si>
-  <si>
-    <t>0.1196,0.3204,0.7675,0.0281</t>
-  </si>
-  <si>
-    <t>0.6655,0.0015,0.0355,0.1789</t>
-  </si>
-  <si>
-    <t>0.0036,0.0112,0.9944,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.0010,0.9957,0.0024</t>
-  </si>
-  <si>
-    <t>0.0086,0.0232,0.9765,0.0103</t>
-  </si>
-  <si>
-    <t>0.0007,0.0024,0.9967,0.0027</t>
-  </si>
-  <si>
-    <t>0.0470,0.0168,0.9361,0.0017</t>
-  </si>
-  <si>
-    <t>0.0010,0.0045,0.9970,0.0008</t>
-  </si>
-  <si>
-    <t>0.0079,0.0048,0.9782,0.0122</t>
-  </si>
-  <si>
-    <t>0.0090,0.0955,0.9761,0.0033</t>
-  </si>
-  <si>
-    <t>0.7458,0.0039,0.2364,0.0235</t>
-  </si>
-  <si>
-    <t>0.9234,0.0010,0.0828,0.0045</t>
-  </si>
-  <si>
-    <t>0.9665,0.0029,0.0194,0.0060</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0017,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0024,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0085,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0010,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9962,0.0025,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.0068,0.9822,0.0033</t>
-  </si>
-  <si>
-    <t>0.0089,0.0201,0.9901,0.0005</t>
-  </si>
-  <si>
-    <t>0.0020,0.0087,0.9922,0.0016</t>
-  </si>
-  <si>
-    <t>0.0105,0.0356,0.9461,0.0130</t>
-  </si>
-  <si>
-    <t>0.0057,0.0006,0.9925,0.0013</t>
-  </si>
-  <si>
-    <t>0.1506,0.0026,0.6650,0.0591</t>
-  </si>
-  <si>
-    <t>0.0614,0.0161,0.9439,0.0067</t>
-  </si>
-  <si>
-    <t>0.0272,0.0004,0.9792,0.0013</t>
-  </si>
-  <si>
-    <t>0.8948,0.0000,0.0002,0.3290</t>
-  </si>
-  <si>
-    <t>0.0361,0.0106,0.0007,0.9865</t>
-  </si>
-  <si>
-    <t>0.0123,0.0020,0.0018,0.9935</t>
+    <t>0.9931,0.0026,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9929,0.0083,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9950,0.0016,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9971,0.0023,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0116,0.0028,0.9816,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.0034,0.9940,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.0063,0.9946,0.0077</t>
+  </si>
+  <si>
+    <t>0.0081,0.0046,0.9835,0.0028</t>
+  </si>
+  <si>
+    <t>0.0019,0.0016,0.9963,0.0008</t>
+  </si>
+  <si>
+    <t>0.9017,0.0009,0.0498,0.0091</t>
+  </si>
+  <si>
+    <t>0.1273,0.0158,0.8917,0.0086</t>
+  </si>
+  <si>
+    <t>0.0134,0.0053,0.9591,0.0328</t>
+  </si>
+  <si>
+    <t>0.9003,0.0006,0.0026,0.1608</t>
+  </si>
+  <si>
+    <t>0.0105,0.0172,0.0011,0.9936</t>
+  </si>
+  <si>
+    <t>0.0316,0.0010,0.0003,0.9906</t>
   </si>
   <si>
     <t>0.0004,0.0001,0.0002,0.9996</t>
   </si>
   <si>
-    <t>0.0007,0.0002,0.0007,0.9993</t>
-  </si>
-  <si>
-    <t>0.9743,0.0014,0.0003,0.0205</t>
+    <t>0.0005,0.0000,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.9963,0.0002,0.0003,0.0016</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2398,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2902,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2986,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3099,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3126,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3154,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>270</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3910,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3994,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4204,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4372,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4638,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4750,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4820,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4876,10 +4888,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5170,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
